--- a/Platform/Platform.WebSite/ModuleResources/Other/SPA_ScoringInfo/ImportTemplates/施工達交狀況盤點頁籤明細匯入範本.xlsx
+++ b/Platform/Platform.WebSite/ModuleResources/Other/SPA_ScoringInfo/ImportTemplates/施工達交狀況盤點頁籤明細匯入範本.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFA868E6-A120-458F-B0D9-AFBF1A456AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\212486\Desktop\供應商評鑑系統\SPA系統優化2.0\UAT\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B12A3E05-EAA9-4A7C-940B-3638C49E97EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="23453" windowHeight="14648" xr2:uid="{2984F46C-2D94-4B4A-AD03-55CBAB69B2C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2984F46C-2D94-4B4A-AD03-55CBAB69B2C2}"/>
   </bookViews>
   <sheets>
     <sheet name="施工達交狀況" sheetId="2" r:id="rId1"/>
@@ -14,17 +19,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="2"/>
@@ -36,15 +30,100 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>tc={5C7F29B1-21DA-4506-AEA6-9EE3A022C1B8}</author>
+    <author>tc={E3B43AF4-0FE9-4B51-BA31-2C52B6C61147}</author>
+    <author>tc={741FBEB8-759E-42C6-9D03-A38EEF36AAB3}</author>
+    <author>tc={B7C152B6-1738-45F7-9978-85701706F46E}</author>
+    <author>tc={8C5CFB61-F86F-4CC5-966B-AEE21BCD7764}</author>
+    <author>tc={EE7BAF57-A807-46D6-95B0-E510D134256D}</author>
+    <author>tc={619CB2ED-6A40-40DD-844E-1C793B0D96EE}</author>
+    <author>tc={747211F6-3B9F-42EA-9D68-78634F00A6CB}</author>
+    <author>tc={C3A62E00-B59F-46B7-B62C-F04FD4A460FF}</author>
+    <author>tc={F8851E16-8D87-42A5-8E3D-AA8A6A50C51F}</author>
+    <author>tc={F0C77876-A406-4B44-A36D-3BE47E6B8BC2}</author>
   </authors>
   <commentList>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{5C7F29B1-21DA-4506-AEA6-9EE3A022C1B8}">
-      <text>
-        <t>[對話串註解]
-您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
-註解:
-    請輸入"Yes” 或 "No"</t>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{E3B43AF4-0FE9-4B51-BA31-2C52B6C61147}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑期間一致</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="1" shapeId="0" xr:uid="{741FBEB8-759E-42C6-9D03-A38EEF36AAB3}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑單位一致</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="2" shapeId="0" xr:uid="{B7C152B6-1738-45F7-9978-85701706F46E}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的服務對象一致</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="3" shapeId="0" xr:uid="{8C5CFB61-F86F-4CC5-966B-AEE21BCD7764}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的評鑑項目一致</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="4" shapeId="0" xr:uid="{EE7BAF57-A807-46D6-95B0-E510D134256D}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    須與系統上的受評供應商一致</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="5" shapeId="0" xr:uid="{619CB2ED-6A40-40DD-844E-1C793B0D96EE}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    機台所屬BU
+評鑑單位為DSS才需要填寫，其餘評鑑單位不用填寫</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="6" shapeId="0" xr:uid="{747211F6-3B9F-42EA-9D68-78634F00A6CB}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    該機台的作業項目
+評鑑單位為DSS才需要填寫，其餘評鑑單位不用填寫</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="7" shapeId="0" xr:uid="{C3A62E00-B59F-46B7-B62C-F04FD4A460FF}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    在評鑑期間有獨立承攬、完工且請款之機台名稱</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="8" shapeId="0" xr:uid="{F8851E16-8D87-42A5-8E3D-AA8A6A50C51F}">
+      <text>
+        <t xml:space="preserve">[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    準時交付，填 'Yes'
+沒有準時交付，填 'No'
+（大小寫必須完全一致；禁止寫 YES/Y/yes 等其他形式） </t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="9" shapeId="0" xr:uid="{F0C77876-A406-4B44-A36D-3BE47E6B8BC2}">
+      <text>
+        <t>[對話串註解]
+您的 Excel 版本可讓您讀取此對話串註解; 但若以較新的 Excel 版本開啟此檔案，將會移除對它進行的所有編輯。深入了解: https://go.microsoft.com/fwlink/?linkid=870924。
+註解:
+    沒有準時交付，請在備註填寫原因</t>
       </text>
     </comment>
   </commentList>
@@ -98,7 +177,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -121,6 +200,17 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -175,7 +265,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -185,6 +275,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -204,7 +295,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="a92573" id="{A633DB54-FF6F-4A3C-AD5A-2EC598405E48}" userId="S::a92573@e365.shop::a5c1d779-7da7-4f72-9b02-b37c31ccf028" providerId="AD"/>
+  <person displayName="TET SCM Chen, Grace" id="{603255D6-0C87-4F13-BB08-A95FE36506D3}" userId="S::grace2.chen@tel.com::6dbe00fd-a5fc-44db-ab99-cd07605e303e" providerId="AD"/>
 </personList>
 </file>
 
@@ -525,24 +616,55 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="J1" dT="2026-07-17T23:26:37.92" personId="{A633DB54-FF6F-4A3C-AD5A-2EC598405E48}" id="{5C7F29B1-21DA-4506-AEA6-9EE3A022C1B8}">
-    <text>請輸入"Yes” 或 "No"</text>
+  <threadedComment ref="A1" dT="2026-09-17T02:57:37.00" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{E3B43AF4-0FE9-4B51-BA31-2C52B6C61147}">
+    <text>須與系統上的評鑑期間一致</text>
+  </threadedComment>
+  <threadedComment ref="B1" dT="2026-09-17T02:57:51.28" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{741FBEB8-759E-42C6-9D03-A38EEF36AAB3}">
+    <text>須與系統上的評鑑單位一致</text>
+  </threadedComment>
+  <threadedComment ref="C1" dT="2026-09-17T02:58:14.38" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{B7C152B6-1738-45F7-9978-85701706F46E}">
+    <text>須與系統上的服務對象一致</text>
+  </threadedComment>
+  <threadedComment ref="D1" dT="2026-09-17T02:58:34.54" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{8C5CFB61-F86F-4CC5-966B-AEE21BCD7764}">
+    <text>須與系統上的評鑑項目一致</text>
+  </threadedComment>
+  <threadedComment ref="E1" dT="2026-09-17T02:58:57.50" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{EE7BAF57-A807-46D6-95B0-E510D134256D}">
+    <text>須與系統上的受評供應商一致</text>
+  </threadedComment>
+  <threadedComment ref="F1" dT="2026-09-17T02:50:44.90" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{619CB2ED-6A40-40DD-844E-1C793B0D96EE}">
+    <text>機台所屬BU
+評鑑單位為DSS才需要填寫，其餘評鑑單位不用填寫</text>
+  </threadedComment>
+  <threadedComment ref="G1" dT="2026-09-17T02:59:57.29" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{747211F6-3B9F-42EA-9D68-78634F00A6CB}">
+    <text>該機台的作業項目
+評鑑單位為DSS才需要填寫，其餘評鑑單位不用填寫</text>
+  </threadedComment>
+  <threadedComment ref="H1" dT="2026-09-23T06:35:09.31" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{C3A62E00-B59F-46B7-B62C-F04FD4A460FF}">
+    <text>在評鑑期間有獨立承攬、完工且請款之機台名稱</text>
+  </threadedComment>
+  <threadedComment ref="J1" dT="2026-09-17T03:02:50.68" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{F8851E16-8D87-42A5-8E3D-AA8A6A50C51F}">
+    <text xml:space="preserve">準時交付，填 'Yes'
+沒有準時交付，填 'No'
+（大小寫必須完全一致；禁止寫 YES/Y/yes 等其他形式） </text>
+  </threadedComment>
+  <threadedComment ref="K1" dT="2026-09-23T06:37:56.54" personId="{603255D6-0C87-4F13-BB08-A95FE36506D3}" id="{F0C77876-A406-4B44-A36D-3BE47E6B8BC2}">
+    <text>沒有準時交付，請在備註填寫原因</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF95FE55-2604-4252-ACB4-E76A09C0D78B}">
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="8" width="15.796875" customWidth="1"/>
+    <col min="1" max="8" width="15.81640625" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="15.796875" customWidth="1"/>
-    <col min="11" max="11" width="25.796875" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" customWidth="1"/>
+    <col min="11" max="11" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.8" customHeight="1">
+    <row r="1" spans="1:11" ht="28.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -576,6 +698,18 @@
       <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
